--- a/data/unmapped_review_first_pass.xlsx
+++ b/data/unmapped_review_first_pass.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="review_queue" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="quick_pick" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="initiative_options" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +33,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="4">
@@ -66,10 +71,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -20606,4 +20612,320 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Initiative Selection Options</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Initiative Classification</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Matrix Category</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tokenized Securities / RWA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Traditional financial assets represented on blockchain rails.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DLT / Blockchain Infrastructure</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Core ledger and platform infrastructure enabling digital asset use cases.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Native digital asset activity and crypto market infrastructure.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Payment Infrastructure</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Payment rail execution including domestic and cross-border flows.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Stablecoins &amp; Deposit Tokens</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fiat-referenced digital money instruments and related workflows.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CBDC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Public Money</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Central bank digital currency pilots, policy, and implementations.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DeFi</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Decentralized Markets</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Decentralized protocol-based financial activity.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Digital Asset Strategy</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Enterprise strategic posture, governance, and capability planning.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Interoperability &amp; Standards</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Standards and mechanisms connecting systems and ledgers.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Settlement Infrastructure</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Market Structure</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Clearing, settlement finality, collateral, and post-trade rails.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Policy</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Regulatory frameworks, supervision, and compliance controls.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cross-Border Payments</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Payments</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Alias mapped to Payment Infrastructure for matrix consistency.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/unmapped_review_first_pass.xlsx
+++ b/data/unmapped_review_first_pass.xlsx
@@ -470,18 +470,18 @@
     <col width="22" customWidth="1" min="23" max="23"/>
     <col width="28" customWidth="1" min="24" max="24"/>
     <col width="60" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="28" customWidth="1" min="27" max="27"/>
+    <col width="21" customWidth="1" min="26" max="26"/>
+    <col width="60" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="14" customWidth="1" min="29" max="29"/>
     <col width="17" customWidth="1" min="30" max="30"/>
-    <col width="15" customWidth="1" min="31" max="31"/>
+    <col width="16" customWidth="1" min="31" max="31"/>
     <col width="18" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="21" customWidth="1" min="34" max="34"/>
-    <col width="16" customWidth="1" min="35" max="35"/>
-    <col width="13" customWidth="1" min="36" max="36"/>
-    <col width="17" customWidth="1" min="37" max="37"/>
+    <col width="27" customWidth="1" min="34" max="34"/>
+    <col width="60" customWidth="1" min="35" max="35"/>
+    <col width="18" customWidth="1" min="36" max="36"/>
+    <col width="22" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -777,18 +777,46 @@
           <t>macro/monetary-policy commentary; recommend re-tier out of Structural</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>RC08_MACRO_COMMENTARY</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC08_MACRO_COMMENTARY)</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -900,18 +928,50 @@
           <t>macro/monetary-policy commentary; recommend re-tier out of Structural</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>RC08_MACRO_COMMENTARY</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC08_MACRO_COMMENTARY)</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1023,18 +1083,50 @@
           <t>macro/monetary-policy commentary; recommend re-tier out of Structural</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>RC08_MACRO_COMMENTARY</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC08_MACRO_COMMENTARY)</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1142,18 +1234,46 @@
           <t>macro/monetary-policy commentary; recommend re-tier out of Structural</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>RC08_MACRO_COMMENTARY</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC08_MACRO_COMMENTARY)</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1261,18 +1381,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1384,18 +1532,50 @@
           <t>macro/monetary-policy commentary; recommend re-tier out of Structural</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>RC08_MACRO_COMMENTARY</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC08_MACRO_COMMENTARY)</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1519,18 +1699,62 @@
           <t>\binteroperabil(?:ity|e)\b|standards?</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Interoperability &amp; Standards|Regulatory / Compliance|DLT / Blockchain Infrastructure</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>dlt</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>dlt-3</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>dlt-3</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>banks_fmis</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>auto-accepted: high-confidence theme + play match</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1642,18 +1866,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1765,18 +2021,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1888,18 +2176,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2011,18 +2331,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2249,18 +2601,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2368,18 +2748,46 @@
           <t>macro/monetary-policy commentary; recommend re-tier out of Structural</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>RC08_MACRO_COMMENTARY</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC08_MACRO_COMMENTARY)</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2491,18 +2899,50 @@
           <t>macro/monetary-policy commentary; recommend re-tier out of Structural</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>RC08_MACRO_COMMENTARY</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC08_MACRO_COMMENTARY)</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2614,18 +3054,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2737,18 +3209,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2979,18 +3483,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3102,18 +3638,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3344,18 +3912,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3586,18 +4186,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3709,18 +4341,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3832,18 +4496,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr"/>
-      <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3955,18 +4651,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="inlineStr"/>
-      <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4074,18 +4802,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4193,18 +4949,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance|Digital Asset Strategy</t>
+        </is>
+      </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
-      <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4312,18 +5100,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="inlineStr"/>
-      <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="inlineStr"/>
-      <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="inlineStr"/>
-      <c r="AJ31" t="inlineStr"/>
-      <c r="AK31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4431,18 +5251,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr"/>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr"/>
-      <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4550,18 +5398,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Digital Asset Strategy</t>
+        </is>
+      </c>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4665,18 +5545,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="inlineStr"/>
-      <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4784,18 +5692,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr"/>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="inlineStr"/>
-      <c r="AJ35" t="inlineStr"/>
-      <c r="AK35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4903,18 +5843,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="inlineStr"/>
-      <c r="AJ36" t="inlineStr"/>
-      <c r="AK36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5018,18 +5986,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr"/>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="inlineStr"/>
-      <c r="AJ37" t="inlineStr"/>
-      <c r="AK37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5141,18 +6137,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="inlineStr"/>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="inlineStr"/>
-      <c r="AJ38" t="inlineStr"/>
-      <c r="AK38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5264,18 +6292,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="inlineStr"/>
       <c r="AE39" t="inlineStr"/>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="inlineStr"/>
-      <c r="AJ39" t="inlineStr"/>
-      <c r="AK39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5387,18 +6447,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="inlineStr"/>
-      <c r="AF40" t="inlineStr"/>
-      <c r="AG40" t="inlineStr"/>
-      <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="inlineStr"/>
-      <c r="AJ40" t="inlineStr"/>
-      <c r="AK40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5625,18 +6717,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr"/>
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="inlineStr"/>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="inlineStr"/>
-      <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="inlineStr"/>
-      <c r="AJ42" t="inlineStr"/>
-      <c r="AK42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5744,18 +6864,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr"/>
       <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="inlineStr"/>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="inlineStr"/>
-      <c r="AH43" t="inlineStr"/>
-      <c r="AI43" t="inlineStr"/>
-      <c r="AJ43" t="inlineStr"/>
-      <c r="AK43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5867,18 +7015,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr"/>
       <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="inlineStr"/>
-      <c r="AF44" t="inlineStr"/>
-      <c r="AG44" t="inlineStr"/>
-      <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="inlineStr"/>
-      <c r="AJ44" t="inlineStr"/>
-      <c r="AK44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5990,18 +7170,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr"/>
       <c r="AD45" t="inlineStr"/>
       <c r="AE45" t="inlineStr"/>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="inlineStr"/>
-      <c r="AH45" t="inlineStr"/>
-      <c r="AI45" t="inlineStr"/>
-      <c r="AJ45" t="inlineStr"/>
-      <c r="AK45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6113,18 +7325,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr"/>
       <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="inlineStr"/>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="inlineStr"/>
-      <c r="AH46" t="inlineStr"/>
-      <c r="AI46" t="inlineStr"/>
-      <c r="AJ46" t="inlineStr"/>
-      <c r="AK46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6232,18 +7476,50 @@
           <t>macro/monetary-policy commentary; recommend re-tier out of Structural</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr"/>
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="inlineStr"/>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="inlineStr"/>
-      <c r="AH47" t="inlineStr"/>
-      <c r="AI47" t="inlineStr"/>
-      <c r="AJ47" t="inlineStr"/>
-      <c r="AK47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>RC08_MACRO_COMMENTARY</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC08_MACRO_COMMENTARY)</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6351,18 +7627,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr"/>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="inlineStr"/>
       <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="inlineStr"/>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="inlineStr"/>
-      <c r="AH48" t="inlineStr"/>
-      <c r="AI48" t="inlineStr"/>
-      <c r="AJ48" t="inlineStr"/>
-      <c r="AK48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6470,18 +7774,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr"/>
       <c r="AD49" t="inlineStr"/>
       <c r="AE49" t="inlineStr"/>
-      <c r="AF49" t="inlineStr"/>
-      <c r="AG49" t="inlineStr"/>
-      <c r="AH49" t="inlineStr"/>
-      <c r="AI49" t="inlineStr"/>
-      <c r="AJ49" t="inlineStr"/>
-      <c r="AK49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6585,18 +7921,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr"/>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr"/>
       <c r="AD50" t="inlineStr"/>
       <c r="AE50" t="inlineStr"/>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="inlineStr"/>
-      <c r="AH50" t="inlineStr"/>
-      <c r="AI50" t="inlineStr"/>
-      <c r="AJ50" t="inlineStr"/>
-      <c r="AK50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6704,18 +8068,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr"/>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr"/>
       <c r="AD51" t="inlineStr"/>
       <c r="AE51" t="inlineStr"/>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="inlineStr"/>
-      <c r="AH51" t="inlineStr"/>
-      <c r="AI51" t="inlineStr"/>
-      <c r="AJ51" t="inlineStr"/>
-      <c r="AK51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6823,18 +8215,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr"/>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="inlineStr"/>
       <c r="AD52" t="inlineStr"/>
       <c r="AE52" t="inlineStr"/>
-      <c r="AF52" t="inlineStr"/>
-      <c r="AG52" t="inlineStr"/>
-      <c r="AH52" t="inlineStr"/>
-      <c r="AI52" t="inlineStr"/>
-      <c r="AJ52" t="inlineStr"/>
-      <c r="AK52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6942,18 +8362,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr"/>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr"/>
       <c r="AD53" t="inlineStr"/>
       <c r="AE53" t="inlineStr"/>
-      <c r="AF53" t="inlineStr"/>
-      <c r="AG53" t="inlineStr"/>
-      <c r="AH53" t="inlineStr"/>
-      <c r="AI53" t="inlineStr"/>
-      <c r="AJ53" t="inlineStr"/>
-      <c r="AK53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7061,18 +8509,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="inlineStr"/>
       <c r="AD54" t="inlineStr"/>
       <c r="AE54" t="inlineStr"/>
-      <c r="AF54" t="inlineStr"/>
-      <c r="AG54" t="inlineStr"/>
-      <c r="AH54" t="inlineStr"/>
-      <c r="AI54" t="inlineStr"/>
-      <c r="AJ54" t="inlineStr"/>
-      <c r="AK54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7184,18 +8664,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr"/>
       <c r="AD55" t="inlineStr"/>
       <c r="AE55" t="inlineStr"/>
-      <c r="AF55" t="inlineStr"/>
-      <c r="AG55" t="inlineStr"/>
-      <c r="AH55" t="inlineStr"/>
-      <c r="AI55" t="inlineStr"/>
-      <c r="AJ55" t="inlineStr"/>
-      <c r="AK55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7307,18 +8819,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr"/>
       <c r="AD56" t="inlineStr"/>
       <c r="AE56" t="inlineStr"/>
-      <c r="AF56" t="inlineStr"/>
-      <c r="AG56" t="inlineStr"/>
-      <c r="AH56" t="inlineStr"/>
-      <c r="AI56" t="inlineStr"/>
-      <c r="AJ56" t="inlineStr"/>
-      <c r="AK56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7430,18 +8974,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr"/>
       <c r="AD57" t="inlineStr"/>
       <c r="AE57" t="inlineStr"/>
-      <c r="AF57" t="inlineStr"/>
-      <c r="AG57" t="inlineStr"/>
-      <c r="AH57" t="inlineStr"/>
-      <c r="AI57" t="inlineStr"/>
-      <c r="AJ57" t="inlineStr"/>
-      <c r="AK57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7553,18 +9129,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="inlineStr"/>
       <c r="AD58" t="inlineStr"/>
       <c r="AE58" t="inlineStr"/>
-      <c r="AF58" t="inlineStr"/>
-      <c r="AG58" t="inlineStr"/>
-      <c r="AH58" t="inlineStr"/>
-      <c r="AI58" t="inlineStr"/>
-      <c r="AJ58" t="inlineStr"/>
-      <c r="AK58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7676,18 +9284,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="inlineStr"/>
       <c r="AD59" t="inlineStr"/>
       <c r="AE59" t="inlineStr"/>
-      <c r="AF59" t="inlineStr"/>
-      <c r="AG59" t="inlineStr"/>
-      <c r="AH59" t="inlineStr"/>
-      <c r="AI59" t="inlineStr"/>
-      <c r="AJ59" t="inlineStr"/>
-      <c r="AK59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7799,18 +9439,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr"/>
       <c r="AD60" t="inlineStr"/>
       <c r="AE60" t="inlineStr"/>
-      <c r="AF60" t="inlineStr"/>
-      <c r="AG60" t="inlineStr"/>
-      <c r="AH60" t="inlineStr"/>
-      <c r="AI60" t="inlineStr"/>
-      <c r="AJ60" t="inlineStr"/>
-      <c r="AK60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8156,18 +9828,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr"/>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr"/>
       <c r="AD63" t="inlineStr"/>
       <c r="AE63" t="inlineStr"/>
-      <c r="AF63" t="inlineStr"/>
-      <c r="AG63" t="inlineStr"/>
-      <c r="AH63" t="inlineStr"/>
-      <c r="AI63" t="inlineStr"/>
-      <c r="AJ63" t="inlineStr"/>
-      <c r="AK63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8271,18 +9971,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr"/>
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr"/>
       <c r="AD64" t="inlineStr"/>
       <c r="AE64" t="inlineStr"/>
-      <c r="AF64" t="inlineStr"/>
-      <c r="AG64" t="inlineStr"/>
-      <c r="AH64" t="inlineStr"/>
-      <c r="AI64" t="inlineStr"/>
-      <c r="AJ64" t="inlineStr"/>
-      <c r="AK64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8390,18 +10118,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr"/>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr"/>
       <c r="AD65" t="inlineStr"/>
       <c r="AE65" t="inlineStr"/>
-      <c r="AF65" t="inlineStr"/>
-      <c r="AG65" t="inlineStr"/>
-      <c r="AH65" t="inlineStr"/>
-      <c r="AI65" t="inlineStr"/>
-      <c r="AJ65" t="inlineStr"/>
-      <c r="AK65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8632,18 +10388,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr"/>
-      <c r="AA67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="inlineStr"/>
       <c r="AD67" t="inlineStr"/>
       <c r="AE67" t="inlineStr"/>
-      <c r="AF67" t="inlineStr"/>
-      <c r="AG67" t="inlineStr"/>
-      <c r="AH67" t="inlineStr"/>
-      <c r="AI67" t="inlineStr"/>
-      <c r="AJ67" t="inlineStr"/>
-      <c r="AK67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8751,18 +10539,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr"/>
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr"/>
       <c r="AD68" t="inlineStr"/>
       <c r="AE68" t="inlineStr"/>
-      <c r="AF68" t="inlineStr"/>
-      <c r="AG68" t="inlineStr"/>
-      <c r="AH68" t="inlineStr"/>
-      <c r="AI68" t="inlineStr"/>
-      <c r="AJ68" t="inlineStr"/>
-      <c r="AK68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8874,18 +10690,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr"/>
-      <c r="AA69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr"/>
       <c r="AD69" t="inlineStr"/>
       <c r="AE69" t="inlineStr"/>
-      <c r="AF69" t="inlineStr"/>
-      <c r="AG69" t="inlineStr"/>
-      <c r="AH69" t="inlineStr"/>
-      <c r="AI69" t="inlineStr"/>
-      <c r="AJ69" t="inlineStr"/>
-      <c r="AK69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8997,18 +10845,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr"/>
-      <c r="AA70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr"/>
       <c r="AD70" t="inlineStr"/>
       <c r="AE70" t="inlineStr"/>
-      <c r="AF70" t="inlineStr"/>
-      <c r="AG70" t="inlineStr"/>
-      <c r="AH70" t="inlineStr"/>
-      <c r="AI70" t="inlineStr"/>
-      <c r="AJ70" t="inlineStr"/>
-      <c r="AK70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9707,18 +11587,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr"/>
-      <c r="AA76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="inlineStr"/>
       <c r="AD76" t="inlineStr"/>
       <c r="AE76" t="inlineStr"/>
-      <c r="AF76" t="inlineStr"/>
-      <c r="AG76" t="inlineStr"/>
-      <c r="AH76" t="inlineStr"/>
-      <c r="AI76" t="inlineStr"/>
-      <c r="AJ76" t="inlineStr"/>
-      <c r="AK76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -9826,18 +11738,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr"/>
-      <c r="AA77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr"/>
       <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="inlineStr"/>
-      <c r="AF77" t="inlineStr"/>
-      <c r="AG77" t="inlineStr"/>
-      <c r="AH77" t="inlineStr"/>
-      <c r="AI77" t="inlineStr"/>
-      <c r="AJ77" t="inlineStr"/>
-      <c r="AK77" t="inlineStr"/>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -9949,18 +11893,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr"/>
-      <c r="AA78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="inlineStr"/>
       <c r="AD78" t="inlineStr"/>
       <c r="AE78" t="inlineStr"/>
-      <c r="AF78" t="inlineStr"/>
-      <c r="AG78" t="inlineStr"/>
-      <c r="AH78" t="inlineStr"/>
-      <c r="AI78" t="inlineStr"/>
-      <c r="AJ78" t="inlineStr"/>
-      <c r="AK78" t="inlineStr"/>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10072,18 +12048,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr"/>
-      <c r="AA79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="inlineStr"/>
       <c r="AD79" t="inlineStr"/>
       <c r="AE79" t="inlineStr"/>
-      <c r="AF79" t="inlineStr"/>
-      <c r="AG79" t="inlineStr"/>
-      <c r="AH79" t="inlineStr"/>
-      <c r="AI79" t="inlineStr"/>
-      <c r="AJ79" t="inlineStr"/>
-      <c r="AK79" t="inlineStr"/>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10203,18 +12211,62 @@
           <t>\binteroperabil(?:ity|e)\b|standards?</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr"/>
-      <c r="AA80" t="inlineStr"/>
-      <c r="AB80" t="inlineStr"/>
-      <c r="AC80" t="inlineStr"/>
-      <c r="AD80" t="inlineStr"/>
-      <c r="AE80" t="inlineStr"/>
-      <c r="AF80" t="inlineStr"/>
-      <c r="AG80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>Interoperability &amp; Standards|DLT / Blockchain Infrastructure</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>dlt</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>dlt-2</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>dlt-2</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>asset_managers</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="AH80" t="inlineStr"/>
-      <c r="AI80" t="inlineStr"/>
-      <c r="AJ80" t="inlineStr"/>
-      <c r="AK80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>auto-accepted: high-confidence theme + play match</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10322,18 +12374,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr"/>
-      <c r="AA81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="inlineStr"/>
       <c r="AD81" t="inlineStr"/>
       <c r="AE81" t="inlineStr"/>
-      <c r="AF81" t="inlineStr"/>
-      <c r="AG81" t="inlineStr"/>
-      <c r="AH81" t="inlineStr"/>
-      <c r="AI81" t="inlineStr"/>
-      <c r="AJ81" t="inlineStr"/>
-      <c r="AK81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10445,18 +12529,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr"/>
-      <c r="AA82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="inlineStr"/>
       <c r="AD82" t="inlineStr"/>
       <c r="AE82" t="inlineStr"/>
-      <c r="AF82" t="inlineStr"/>
-      <c r="AG82" t="inlineStr"/>
-      <c r="AH82" t="inlineStr"/>
-      <c r="AI82" t="inlineStr"/>
-      <c r="AJ82" t="inlineStr"/>
-      <c r="AK82" t="inlineStr"/>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10568,18 +12684,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr"/>
-      <c r="AA83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="inlineStr"/>
       <c r="AD83" t="inlineStr"/>
       <c r="AE83" t="inlineStr"/>
-      <c r="AF83" t="inlineStr"/>
-      <c r="AG83" t="inlineStr"/>
-      <c r="AH83" t="inlineStr"/>
-      <c r="AI83" t="inlineStr"/>
-      <c r="AJ83" t="inlineStr"/>
-      <c r="AK83" t="inlineStr"/>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10921,18 +13069,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr"/>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr"/>
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="inlineStr"/>
       <c r="AD86" t="inlineStr"/>
       <c r="AE86" t="inlineStr"/>
-      <c r="AF86" t="inlineStr"/>
-      <c r="AG86" t="inlineStr"/>
-      <c r="AH86" t="inlineStr"/>
-      <c r="AI86" t="inlineStr"/>
-      <c r="AJ86" t="inlineStr"/>
-      <c r="AK86" t="inlineStr"/>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -11040,18 +13216,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr"/>
-      <c r="AA87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="inlineStr"/>
       <c r="AD87" t="inlineStr"/>
       <c r="AE87" t="inlineStr"/>
-      <c r="AF87" t="inlineStr"/>
-      <c r="AG87" t="inlineStr"/>
-      <c r="AH87" t="inlineStr"/>
-      <c r="AI87" t="inlineStr"/>
-      <c r="AJ87" t="inlineStr"/>
-      <c r="AK87" t="inlineStr"/>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -11282,18 +13490,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr"/>
-      <c r="AA89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="inlineStr"/>
       <c r="AD89" t="inlineStr"/>
       <c r="AE89" t="inlineStr"/>
-      <c r="AF89" t="inlineStr"/>
-      <c r="AG89" t="inlineStr"/>
-      <c r="AH89" t="inlineStr"/>
-      <c r="AI89" t="inlineStr"/>
-      <c r="AJ89" t="inlineStr"/>
-      <c r="AK89" t="inlineStr"/>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -11401,18 +13641,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr"/>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr"/>
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="inlineStr"/>
       <c r="AD90" t="inlineStr"/>
       <c r="AE90" t="inlineStr"/>
-      <c r="AF90" t="inlineStr"/>
-      <c r="AG90" t="inlineStr"/>
-      <c r="AH90" t="inlineStr"/>
-      <c r="AI90" t="inlineStr"/>
-      <c r="AJ90" t="inlineStr"/>
-      <c r="AK90" t="inlineStr"/>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -11520,18 +13788,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr"/>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr"/>
       <c r="AB91" t="inlineStr"/>
       <c r="AC91" t="inlineStr"/>
       <c r="AD91" t="inlineStr"/>
       <c r="AE91" t="inlineStr"/>
-      <c r="AF91" t="inlineStr"/>
-      <c r="AG91" t="inlineStr"/>
-      <c r="AH91" t="inlineStr"/>
-      <c r="AI91" t="inlineStr"/>
-      <c r="AJ91" t="inlineStr"/>
-      <c r="AK91" t="inlineStr"/>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -11758,18 +14054,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr"/>
-      <c r="AA93" t="inlineStr"/>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB93" t="inlineStr"/>
       <c r="AC93" t="inlineStr"/>
       <c r="AD93" t="inlineStr"/>
       <c r="AE93" t="inlineStr"/>
-      <c r="AF93" t="inlineStr"/>
-      <c r="AG93" t="inlineStr"/>
-      <c r="AH93" t="inlineStr"/>
-      <c r="AI93" t="inlineStr"/>
-      <c r="AJ93" t="inlineStr"/>
-      <c r="AK93" t="inlineStr"/>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -11881,18 +14209,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr"/>
-      <c r="AA94" t="inlineStr"/>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB94" t="inlineStr"/>
       <c r="AC94" t="inlineStr"/>
       <c r="AD94" t="inlineStr"/>
       <c r="AE94" t="inlineStr"/>
-      <c r="AF94" t="inlineStr"/>
-      <c r="AG94" t="inlineStr"/>
-      <c r="AH94" t="inlineStr"/>
-      <c r="AI94" t="inlineStr"/>
-      <c r="AJ94" t="inlineStr"/>
-      <c r="AK94" t="inlineStr"/>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -12115,18 +14475,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr"/>
-      <c r="AA96" t="inlineStr"/>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="inlineStr"/>
       <c r="AD96" t="inlineStr"/>
       <c r="AE96" t="inlineStr"/>
-      <c r="AF96" t="inlineStr"/>
-      <c r="AG96" t="inlineStr"/>
-      <c r="AH96" t="inlineStr"/>
-      <c r="AI96" t="inlineStr"/>
-      <c r="AJ96" t="inlineStr"/>
-      <c r="AK96" t="inlineStr"/>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -12234,18 +14626,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr"/>
-      <c r="AA97" t="inlineStr"/>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="inlineStr"/>
       <c r="AD97" t="inlineStr"/>
       <c r="AE97" t="inlineStr"/>
-      <c r="AF97" t="inlineStr"/>
-      <c r="AG97" t="inlineStr"/>
-      <c r="AH97" t="inlineStr"/>
-      <c r="AI97" t="inlineStr"/>
-      <c r="AJ97" t="inlineStr"/>
-      <c r="AK97" t="inlineStr"/>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -12353,18 +14777,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr"/>
-      <c r="AA98" t="inlineStr"/>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="inlineStr"/>
       <c r="AD98" t="inlineStr"/>
       <c r="AE98" t="inlineStr"/>
-      <c r="AF98" t="inlineStr"/>
-      <c r="AG98" t="inlineStr"/>
-      <c r="AH98" t="inlineStr"/>
-      <c r="AI98" t="inlineStr"/>
-      <c r="AJ98" t="inlineStr"/>
-      <c r="AK98" t="inlineStr"/>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -12591,18 +15047,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr"/>
-      <c r="AA100" t="inlineStr"/>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB100" t="inlineStr"/>
       <c r="AC100" t="inlineStr"/>
       <c r="AD100" t="inlineStr"/>
       <c r="AE100" t="inlineStr"/>
-      <c r="AF100" t="inlineStr"/>
-      <c r="AG100" t="inlineStr"/>
-      <c r="AH100" t="inlineStr"/>
-      <c r="AI100" t="inlineStr"/>
-      <c r="AJ100" t="inlineStr"/>
-      <c r="AK100" t="inlineStr"/>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -12710,18 +15198,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr"/>
-      <c r="AA101" t="inlineStr"/>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB101" t="inlineStr"/>
       <c r="AC101" t="inlineStr"/>
       <c r="AD101" t="inlineStr"/>
       <c r="AE101" t="inlineStr"/>
-      <c r="AF101" t="inlineStr"/>
-      <c r="AG101" t="inlineStr"/>
-      <c r="AH101" t="inlineStr"/>
-      <c r="AI101" t="inlineStr"/>
-      <c r="AJ101" t="inlineStr"/>
-      <c r="AK101" t="inlineStr"/>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -13067,18 +15587,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr"/>
-      <c r="AA104" t="inlineStr"/>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="inlineStr"/>
       <c r="AD104" t="inlineStr"/>
       <c r="AE104" t="inlineStr"/>
-      <c r="AF104" t="inlineStr"/>
-      <c r="AG104" t="inlineStr"/>
-      <c r="AH104" t="inlineStr"/>
-      <c r="AI104" t="inlineStr"/>
-      <c r="AJ104" t="inlineStr"/>
-      <c r="AK104" t="inlineStr"/>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -13190,18 +15742,50 @@
           <t>macro/monetary-policy commentary; recommend re-tier out of Structural</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr"/>
-      <c r="AA105" t="inlineStr"/>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB105" t="inlineStr"/>
       <c r="AC105" t="inlineStr"/>
       <c r="AD105" t="inlineStr"/>
       <c r="AE105" t="inlineStr"/>
-      <c r="AF105" t="inlineStr"/>
-      <c r="AG105" t="inlineStr"/>
-      <c r="AH105" t="inlineStr"/>
-      <c r="AI105" t="inlineStr"/>
-      <c r="AJ105" t="inlineStr"/>
-      <c r="AK105" t="inlineStr"/>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>RC08_MACRO_COMMENTARY</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC08_MACRO_COMMENTARY)</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -13309,18 +15893,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr"/>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr"/>
       <c r="AB106" t="inlineStr"/>
       <c r="AC106" t="inlineStr"/>
       <c r="AD106" t="inlineStr"/>
       <c r="AE106" t="inlineStr"/>
-      <c r="AF106" t="inlineStr"/>
-      <c r="AG106" t="inlineStr"/>
-      <c r="AH106" t="inlineStr"/>
-      <c r="AI106" t="inlineStr"/>
-      <c r="AJ106" t="inlineStr"/>
-      <c r="AK106" t="inlineStr"/>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -13551,18 +16163,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr"/>
-      <c r="AA108" t="inlineStr"/>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="inlineStr"/>
       <c r="AD108" t="inlineStr"/>
       <c r="AE108" t="inlineStr"/>
-      <c r="AF108" t="inlineStr"/>
-      <c r="AG108" t="inlineStr"/>
-      <c r="AH108" t="inlineStr"/>
-      <c r="AI108" t="inlineStr"/>
-      <c r="AJ108" t="inlineStr"/>
-      <c r="AK108" t="inlineStr"/>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -13674,18 +16318,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr"/>
-      <c r="AA109" t="inlineStr"/>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB109" t="inlineStr"/>
       <c r="AC109" t="inlineStr"/>
       <c r="AD109" t="inlineStr"/>
       <c r="AE109" t="inlineStr"/>
-      <c r="AF109" t="inlineStr"/>
-      <c r="AG109" t="inlineStr"/>
-      <c r="AH109" t="inlineStr"/>
-      <c r="AI109" t="inlineStr"/>
-      <c r="AJ109" t="inlineStr"/>
-      <c r="AK109" t="inlineStr"/>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -14031,18 +16707,50 @@
           <t>regulatory/perimeter signal with no current theme fit</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr"/>
-      <c r="AA112" t="inlineStr"/>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>candidate_new_theme</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB112" t="inlineStr"/>
       <c r="AC112" t="inlineStr"/>
       <c r="AD112" t="inlineStr"/>
       <c r="AE112" t="inlineStr"/>
-      <c r="AF112" t="inlineStr"/>
-      <c r="AG112" t="inlineStr"/>
-      <c r="AH112" t="inlineStr"/>
-      <c r="AI112" t="inlineStr"/>
-      <c r="AJ112" t="inlineStr"/>
-      <c r="AK112" t="inlineStr"/>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>RC09_REGULATORY_PERIMETER</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>auto-held: regulatory perimeter signal pending future 4th theme</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -14388,18 +17096,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr"/>
-      <c r="AA115" t="inlineStr"/>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB115" t="inlineStr"/>
       <c r="AC115" t="inlineStr"/>
       <c r="AD115" t="inlineStr"/>
       <c r="AE115" t="inlineStr"/>
-      <c r="AF115" t="inlineStr"/>
-      <c r="AG115" t="inlineStr"/>
-      <c r="AH115" t="inlineStr"/>
-      <c r="AI115" t="inlineStr"/>
-      <c r="AJ115" t="inlineStr"/>
-      <c r="AK115" t="inlineStr"/>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -14737,18 +17477,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr"/>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr"/>
       <c r="AB118" t="inlineStr"/>
       <c r="AC118" t="inlineStr"/>
       <c r="AD118" t="inlineStr"/>
       <c r="AE118" t="inlineStr"/>
-      <c r="AF118" t="inlineStr"/>
-      <c r="AG118" t="inlineStr"/>
-      <c r="AH118" t="inlineStr"/>
-      <c r="AI118" t="inlineStr"/>
-      <c r="AJ118" t="inlineStr"/>
-      <c r="AK118" t="inlineStr"/>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -15455,18 +18223,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr"/>
-      <c r="AA124" t="inlineStr"/>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB124" t="inlineStr"/>
       <c r="AC124" t="inlineStr"/>
       <c r="AD124" t="inlineStr"/>
       <c r="AE124" t="inlineStr"/>
-      <c r="AF124" t="inlineStr"/>
-      <c r="AG124" t="inlineStr"/>
-      <c r="AH124" t="inlineStr"/>
-      <c r="AI124" t="inlineStr"/>
-      <c r="AJ124" t="inlineStr"/>
-      <c r="AK124" t="inlineStr"/>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -15570,18 +18370,50 @@
           <t>macro/monetary-policy commentary; recommend re-tier out of Structural</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr"/>
-      <c r="AA125" t="inlineStr"/>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB125" t="inlineStr"/>
       <c r="AC125" t="inlineStr"/>
       <c r="AD125" t="inlineStr"/>
       <c r="AE125" t="inlineStr"/>
-      <c r="AF125" t="inlineStr"/>
-      <c r="AG125" t="inlineStr"/>
-      <c r="AH125" t="inlineStr"/>
-      <c r="AI125" t="inlineStr"/>
-      <c r="AJ125" t="inlineStr"/>
-      <c r="AK125" t="inlineStr"/>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>RC08_MACRO_COMMENTARY</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC08_MACRO_COMMENTARY)</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -15812,18 +18644,62 @@
           <t>\binteroperabil(?:ity|e)\b|standards?</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr"/>
-      <c r="AA127" t="inlineStr"/>
-      <c r="AB127" t="inlineStr"/>
-      <c r="AC127" t="inlineStr"/>
-      <c r="AD127" t="inlineStr"/>
-      <c r="AE127" t="inlineStr"/>
-      <c r="AF127" t="inlineStr"/>
-      <c r="AG127" t="inlineStr"/>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>Interoperability &amp; Standards|Crypto / Digital Assets|DLT / Blockchain Infrastructure</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>dlt</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>dlt-1</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>dlt-1</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>banks_fmis</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="AH127" t="inlineStr"/>
-      <c r="AI127" t="inlineStr"/>
-      <c r="AJ127" t="inlineStr"/>
-      <c r="AK127" t="inlineStr"/>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>auto-accepted: high-confidence theme + play match</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -16641,18 +19517,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr"/>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr"/>
       <c r="AB134" t="inlineStr"/>
       <c r="AC134" t="inlineStr"/>
       <c r="AD134" t="inlineStr"/>
       <c r="AE134" t="inlineStr"/>
-      <c r="AF134" t="inlineStr"/>
-      <c r="AG134" t="inlineStr"/>
-      <c r="AH134" t="inlineStr"/>
-      <c r="AI134" t="inlineStr"/>
-      <c r="AJ134" t="inlineStr"/>
-      <c r="AK134" t="inlineStr"/>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG134" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH134" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -16974,18 +19878,46 @@
           <t>macro/monetary-policy commentary; recommend re-tier out of Structural</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr"/>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr"/>
       <c r="AB137" t="inlineStr"/>
       <c r="AC137" t="inlineStr"/>
       <c r="AD137" t="inlineStr"/>
       <c r="AE137" t="inlineStr"/>
-      <c r="AF137" t="inlineStr"/>
-      <c r="AG137" t="inlineStr"/>
-      <c r="AH137" t="inlineStr"/>
-      <c r="AI137" t="inlineStr"/>
-      <c r="AJ137" t="inlineStr"/>
-      <c r="AK137" t="inlineStr"/>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>RC08_MACRO_COMMENTARY</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC08_MACRO_COMMENTARY)</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -17105,18 +20037,62 @@
           <t>\binteroperabil(?:ity|e)\b|standards?</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr"/>
-      <c r="AA138" t="inlineStr"/>
-      <c r="AB138" t="inlineStr"/>
-      <c r="AC138" t="inlineStr"/>
-      <c r="AD138" t="inlineStr"/>
-      <c r="AE138" t="inlineStr"/>
-      <c r="AF138" t="inlineStr"/>
-      <c r="AG138" t="inlineStr"/>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>Interoperability &amp; Standards|DLT / Blockchain Infrastructure</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>dlt</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>dlt-1</t>
+        </is>
+      </c>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>dlt-1</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>banks_fmis</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="AH138" t="inlineStr"/>
-      <c r="AI138" t="inlineStr"/>
-      <c r="AJ138" t="inlineStr"/>
-      <c r="AK138" t="inlineStr"/>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>auto-accepted: high-confidence theme + play match</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -17236,18 +20212,62 @@
           <t>\binteroperabil(?:ity|e)\b|standards?</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr"/>
-      <c r="AA139" t="inlineStr"/>
-      <c r="AB139" t="inlineStr"/>
-      <c r="AC139" t="inlineStr"/>
-      <c r="AD139" t="inlineStr"/>
-      <c r="AE139" t="inlineStr"/>
-      <c r="AF139" t="inlineStr"/>
-      <c r="AG139" t="inlineStr"/>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>Interoperability &amp; Standards|DLT / Blockchain Infrastructure</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>dlt</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>dlt-1</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>dlt-1</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>banks_fmis</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="AH139" t="inlineStr"/>
-      <c r="AI139" t="inlineStr"/>
-      <c r="AJ139" t="inlineStr"/>
-      <c r="AK139" t="inlineStr"/>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>auto-accepted: high-confidence theme + play match</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -17371,18 +20391,62 @@
           <t>\binteroperabil(?:ity|e)\b|standards?</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr"/>
-      <c r="AA140" t="inlineStr"/>
-      <c r="AB140" t="inlineStr"/>
-      <c r="AC140" t="inlineStr"/>
-      <c r="AD140" t="inlineStr"/>
-      <c r="AE140" t="inlineStr"/>
-      <c r="AF140" t="inlineStr"/>
-      <c r="AG140" t="inlineStr"/>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>Interoperability &amp; Standards|DLT / Blockchain Infrastructure</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>dlt</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>dlt-1</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>dlt-1</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>banks_fmis</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="AH140" t="inlineStr"/>
-      <c r="AI140" t="inlineStr"/>
-      <c r="AJ140" t="inlineStr"/>
-      <c r="AK140" t="inlineStr"/>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>auto-accepted: high-confidence theme + play match</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -17835,18 +20899,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr"/>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr"/>
       <c r="AB144" t="inlineStr"/>
       <c r="AC144" t="inlineStr"/>
       <c r="AD144" t="inlineStr"/>
       <c r="AE144" t="inlineStr"/>
-      <c r="AF144" t="inlineStr"/>
-      <c r="AG144" t="inlineStr"/>
-      <c r="AH144" t="inlineStr"/>
-      <c r="AI144" t="inlineStr"/>
-      <c r="AJ144" t="inlineStr"/>
-      <c r="AK144" t="inlineStr"/>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -18676,18 +21768,62 @@
           <t>\binteroperabil(?:ity|e)\b|standards?</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr"/>
-      <c r="AA151" t="inlineStr"/>
-      <c r="AB151" t="inlineStr"/>
-      <c r="AC151" t="inlineStr"/>
-      <c r="AD151" t="inlineStr"/>
-      <c r="AE151" t="inlineStr"/>
-      <c r="AF151" t="inlineStr"/>
-      <c r="AG151" t="inlineStr"/>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>Interoperability &amp; Standards|DLT / Blockchain Infrastructure</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>dlt</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>dlt-1</t>
+        </is>
+      </c>
+      <c r="AD151" t="inlineStr">
+        <is>
+          <t>dlt-1</t>
+        </is>
+      </c>
+      <c r="AE151" t="inlineStr">
+        <is>
+          <t>banks_fmis</t>
+        </is>
+      </c>
+      <c r="AF151" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="AG151" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="AH151" t="inlineStr"/>
-      <c r="AI151" t="inlineStr"/>
-      <c r="AJ151" t="inlineStr"/>
-      <c r="AK151" t="inlineStr"/>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>auto-accepted: high-confidence theme + play match</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -19382,18 +22518,50 @@
           <t>macro/monetary-policy commentary; recommend re-tier out of Structural</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr"/>
-      <c r="AA157" t="inlineStr"/>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB157" t="inlineStr"/>
       <c r="AC157" t="inlineStr"/>
       <c r="AD157" t="inlineStr"/>
       <c r="AE157" t="inlineStr"/>
-      <c r="AF157" t="inlineStr"/>
-      <c r="AG157" t="inlineStr"/>
-      <c r="AH157" t="inlineStr"/>
-      <c r="AI157" t="inlineStr"/>
-      <c r="AJ157" t="inlineStr"/>
-      <c r="AK157" t="inlineStr"/>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>RC08_MACRO_COMMENTARY</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC08_MACRO_COMMENTARY)</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -19497,18 +22665,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr"/>
-      <c r="AA158" t="inlineStr"/>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB158" t="inlineStr"/>
       <c r="AC158" t="inlineStr"/>
       <c r="AD158" t="inlineStr"/>
       <c r="AE158" t="inlineStr"/>
-      <c r="AF158" t="inlineStr"/>
-      <c r="AG158" t="inlineStr"/>
-      <c r="AH158" t="inlineStr"/>
-      <c r="AI158" t="inlineStr"/>
-      <c r="AJ158" t="inlineStr"/>
-      <c r="AK158" t="inlineStr"/>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -20540,18 +23740,46 @@
           <t>macro/monetary-policy commentary; recommend re-tier out of Structural</t>
         </is>
       </c>
-      <c r="Z167" t="inlineStr"/>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr"/>
       <c r="AB167" t="inlineStr"/>
       <c r="AC167" t="inlineStr"/>
       <c r="AD167" t="inlineStr"/>
       <c r="AE167" t="inlineStr"/>
-      <c r="AF167" t="inlineStr"/>
-      <c r="AG167" t="inlineStr"/>
-      <c r="AH167" t="inlineStr"/>
-      <c r="AI167" t="inlineStr"/>
-      <c r="AJ167" t="inlineStr"/>
-      <c r="AK167" t="inlineStr"/>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>RC08_MACRO_COMMENTARY</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC08_MACRO_COMMENTARY)</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -21825,18 +25053,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z178" t="inlineStr"/>
-      <c r="AA178" t="inlineStr"/>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB178" t="inlineStr"/>
       <c r="AC178" t="inlineStr"/>
       <c r="AD178" t="inlineStr"/>
       <c r="AE178" t="inlineStr"/>
-      <c r="AF178" t="inlineStr"/>
-      <c r="AG178" t="inlineStr"/>
-      <c r="AH178" t="inlineStr"/>
-      <c r="AI178" t="inlineStr"/>
-      <c r="AJ178" t="inlineStr"/>
-      <c r="AK178" t="inlineStr"/>
+      <c r="AF178" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG178" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH178" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI178" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ178" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK178" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -22067,18 +25327,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z180" t="inlineStr"/>
-      <c r="AA180" t="inlineStr"/>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB180" t="inlineStr"/>
       <c r="AC180" t="inlineStr"/>
       <c r="AD180" t="inlineStr"/>
       <c r="AE180" t="inlineStr"/>
-      <c r="AF180" t="inlineStr"/>
-      <c r="AG180" t="inlineStr"/>
-      <c r="AH180" t="inlineStr"/>
-      <c r="AI180" t="inlineStr"/>
-      <c r="AJ180" t="inlineStr"/>
-      <c r="AK180" t="inlineStr"/>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -23590,18 +26882,62 @@
           <t>\binteroperabil(?:ity|e)\b|standards?</t>
         </is>
       </c>
-      <c r="Z193" t="inlineStr"/>
-      <c r="AA193" t="inlineStr"/>
-      <c r="AB193" t="inlineStr"/>
-      <c r="AC193" t="inlineStr"/>
-      <c r="AD193" t="inlineStr"/>
-      <c r="AE193" t="inlineStr"/>
-      <c r="AF193" t="inlineStr"/>
-      <c r="AG193" t="inlineStr"/>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>Interoperability &amp; Standards|Regulatory / Compliance|DLT / Blockchain Infrastructure</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>dlt</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>dlt-1</t>
+        </is>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>dlt-1</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>banks_fmis</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="AH193" t="inlineStr"/>
-      <c r="AI193" t="inlineStr"/>
-      <c r="AJ193" t="inlineStr"/>
-      <c r="AK193" t="inlineStr"/>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>auto-accepted: high-confidence theme + play match</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -23709,18 +27045,46 @@
           <t>insufficient keyword or workflow evidence</t>
         </is>
       </c>
-      <c r="Z194" t="inlineStr"/>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
       <c r="AA194" t="inlineStr"/>
       <c r="AB194" t="inlineStr"/>
       <c r="AC194" t="inlineStr"/>
       <c r="AD194" t="inlineStr"/>
       <c r="AE194" t="inlineStr"/>
-      <c r="AF194" t="inlineStr"/>
-      <c r="AG194" t="inlineStr"/>
-      <c r="AH194" t="inlineStr"/>
-      <c r="AI194" t="inlineStr"/>
-      <c r="AJ194" t="inlineStr"/>
-      <c r="AK194" t="inlineStr"/>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -24078,18 +27442,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z197" t="inlineStr"/>
-      <c r="AA197" t="inlineStr"/>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>Crypto / Digital Assets</t>
+        </is>
+      </c>
       <c r="AB197" t="inlineStr"/>
       <c r="AC197" t="inlineStr"/>
       <c r="AD197" t="inlineStr"/>
       <c r="AE197" t="inlineStr"/>
-      <c r="AF197" t="inlineStr"/>
-      <c r="AG197" t="inlineStr"/>
-      <c r="AH197" t="inlineStr"/>
-      <c r="AI197" t="inlineStr"/>
-      <c r="AJ197" t="inlineStr"/>
-      <c r="AK197" t="inlineStr"/>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -25510,18 +28906,62 @@
           <t>\binteroperabil(?:ity|e)\b|standards?</t>
         </is>
       </c>
-      <c r="Z209" t="inlineStr"/>
-      <c r="AA209" t="inlineStr"/>
-      <c r="AB209" t="inlineStr"/>
-      <c r="AC209" t="inlineStr"/>
-      <c r="AD209" t="inlineStr"/>
-      <c r="AE209" t="inlineStr"/>
-      <c r="AF209" t="inlineStr"/>
-      <c r="AG209" t="inlineStr"/>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>Interoperability &amp; Standards|Regulatory / Compliance|DLT / Blockchain Infrastructure</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>dlt</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>dlt-1</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>dlt-1</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>banks_fmis</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="AH209" t="inlineStr"/>
-      <c r="AI209" t="inlineStr"/>
-      <c r="AJ209" t="inlineStr"/>
-      <c r="AK209" t="inlineStr"/>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>auto-accepted: high-confidence theme + play match</t>
+        </is>
+      </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -25641,18 +29081,62 @@
           <t>\binteroperabil(?:ity|e)\b|standards?</t>
         </is>
       </c>
-      <c r="Z210" t="inlineStr"/>
-      <c r="AA210" t="inlineStr"/>
-      <c r="AB210" t="inlineStr"/>
-      <c r="AC210" t="inlineStr"/>
-      <c r="AD210" t="inlineStr"/>
-      <c r="AE210" t="inlineStr"/>
-      <c r="AF210" t="inlineStr"/>
-      <c r="AG210" t="inlineStr"/>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>Interoperability &amp; Standards|DLT / Blockchain Infrastructure</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>dlt</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>dlt-1</t>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>dlt-1</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>banks_fmis</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="AH210" t="inlineStr"/>
-      <c r="AI210" t="inlineStr"/>
-      <c r="AJ210" t="inlineStr"/>
-      <c r="AK210" t="inlineStr"/>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>auto-accepted: high-confidence theme + play match</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -26129,18 +29613,50 @@
           <t>weak theme fit; review initiative-level multi-label suggestion</t>
         </is>
       </c>
-      <c r="Z214" t="inlineStr"/>
-      <c r="AA214" t="inlineStr"/>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>keep_unmapped</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>Regulatory / Compliance</t>
+        </is>
+      </c>
       <c r="AB214" t="inlineStr"/>
       <c r="AC214" t="inlineStr"/>
       <c r="AD214" t="inlineStr"/>
       <c r="AE214" t="inlineStr"/>
-      <c r="AF214" t="inlineStr"/>
-      <c r="AG214" t="inlineStr"/>
-      <c r="AH214" t="inlineStr"/>
-      <c r="AI214" t="inlineStr"/>
-      <c r="AJ214" t="inlineStr"/>
-      <c r="AK214" t="inlineStr"/>
+      <c r="AF214" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AG214" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="AH214" t="inlineStr">
+        <is>
+          <t>RC03_NATIVE_CRYPTO_ONLY</t>
+        </is>
+      </c>
+      <c r="AI214" t="inlineStr">
+        <is>
+          <t>auto-closed: reliable-noise classification (RC03_NATIVE_CRYPTO_ONLY)</t>
+        </is>
+      </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -26399,18 +29915,62 @@
           <t>\binteroperabil(?:ity|e)\b|standards?</t>
         </is>
       </c>
-      <c r="Z216" t="inlineStr"/>
-      <c r="AA216" t="inlineStr"/>
-      <c r="AB216" t="inlineStr"/>
-      <c r="AC216" t="inlineStr"/>
-      <c r="AD216" t="inlineStr"/>
-      <c r="AE216" t="inlineStr"/>
-      <c r="AF216" t="inlineStr"/>
-      <c r="AG216" t="inlineStr"/>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>Interoperability &amp; Standards|Regulatory / Compliance|DLT / Blockchain Infrastructure</t>
+        </is>
+      </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>dlt</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>dlt-1</t>
+        </is>
+      </c>
+      <c r="AD216" t="inlineStr">
+        <is>
+          <t>dlt-1</t>
+        </is>
+      </c>
+      <c r="AE216" t="inlineStr">
+        <is>
+          <t>banks_fmis</t>
+        </is>
+      </c>
+      <c r="AF216" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="AG216" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="AH216" t="inlineStr"/>
-      <c r="AI216" t="inlineStr"/>
-      <c r="AJ216" t="inlineStr"/>
-      <c r="AK216" t="inlineStr"/>
+      <c r="AI216" t="inlineStr">
+        <is>
+          <t>auto-accepted: high-confidence theme + play match</t>
+        </is>
+      </c>
+      <c r="AJ216" t="inlineStr">
+        <is>
+          <t>auto_accepter_v1</t>
+        </is>
+      </c>
+      <c r="AK216" t="inlineStr">
+        <is>
+          <t>2026-05-10T08:01:33Z</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
